--- a/tensile_strength_clammp.xlsx
+++ b/tensile_strength_clammp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/mjl9889_ads_northwestern_edu/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/graphene-oxide-paper-coatings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="152" documentId="8_{E7047EFC-AC87-1446-9EE2-AFD11443121C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{455755F8-22ED-4B4B-AE63-DDA44C614B8A}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="8_{E7047EFC-AC87-1446-9EE2-AFD11443121C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B449AC5C-D5B9-F249-8F15-DFA47597011A}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="1240" windowWidth="27640" windowHeight="16740" xr2:uid="{9D6F6D14-15C4-894F-A380-C8BF75B569C1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="19">
   <si>
     <t>Sample</t>
   </si>
@@ -88,15 +88,21 @@
   <si>
     <t>Small</t>
   </si>
+  <si>
+    <t>25% WBBC</t>
+  </si>
+  <si>
+    <t>25% WBBC + 0.1% GO</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -109,6 +115,12 @@
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -131,10 +143,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="5"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -469,13 +484,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1161D6ED-F005-7245-AC8F-CA8CEF89B76D}">
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
@@ -2378,6 +2394,346 @@
         <v>58.115642999999999</v>
       </c>
     </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96">
+        <v>1</v>
+      </c>
+      <c r="B96" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" s="3">
+        <v>167.13777200000001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97">
+        <v>2</v>
+      </c>
+      <c r="B97" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" s="3">
+        <v>183.36656199999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98">
+        <v>3</v>
+      </c>
+      <c r="B98" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" t="s">
+        <v>17</v>
+      </c>
+      <c r="D98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E98" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="3">
+        <v>172.92344700000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99">
+        <v>4</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" t="s">
+        <v>17</v>
+      </c>
+      <c r="D99" t="s">
+        <v>8</v>
+      </c>
+      <c r="E99" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" s="3">
+        <v>154.911407</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" s="3">
+        <v>185.175613</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101">
+        <v>6</v>
+      </c>
+      <c r="B101" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="3">
+        <v>181.60211200000001</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102">
+        <v>7</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="3">
+        <v>194.250381</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103">
+        <v>8</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" t="s">
+        <v>17</v>
+      </c>
+      <c r="D103" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" s="3">
+        <v>196.03801000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104">
+        <v>9</v>
+      </c>
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" t="s">
+        <v>17</v>
+      </c>
+      <c r="D104" t="s">
+        <v>8</v>
+      </c>
+      <c r="E104" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" s="3">
+        <v>163.556961</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105">
+        <v>1</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" t="s">
+        <v>18</v>
+      </c>
+      <c r="D105" t="s">
+        <v>8</v>
+      </c>
+      <c r="E105" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" s="1">
+        <v>179.52157600000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106">
+        <v>2</v>
+      </c>
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" t="s">
+        <v>8</v>
+      </c>
+      <c r="E106" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="1">
+        <v>183.438705</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107">
+        <v>3</v>
+      </c>
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" t="s">
+        <v>18</v>
+      </c>
+      <c r="D107" t="s">
+        <v>8</v>
+      </c>
+      <c r="E107" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="1">
+        <v>192.07661400000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108">
+        <v>4</v>
+      </c>
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" t="s">
+        <v>18</v>
+      </c>
+      <c r="D108" t="s">
+        <v>8</v>
+      </c>
+      <c r="E108" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" s="1">
+        <v>184.39044200000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109">
+        <v>5</v>
+      </c>
+      <c r="B109" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" t="s">
+        <v>18</v>
+      </c>
+      <c r="D109" t="s">
+        <v>8</v>
+      </c>
+      <c r="E109" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" s="1">
+        <v>179.04513499999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110">
+        <v>6</v>
+      </c>
+      <c r="B110" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" t="s">
+        <v>18</v>
+      </c>
+      <c r="D110" t="s">
+        <v>8</v>
+      </c>
+      <c r="E110" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="1">
+        <v>173.60133400000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111">
+        <v>7</v>
+      </c>
+      <c r="B111" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" t="s">
+        <v>18</v>
+      </c>
+      <c r="D111" t="s">
+        <v>8</v>
+      </c>
+      <c r="E111" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="1">
+        <v>178.69653299999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112">
+        <v>8</v>
+      </c>
+      <c r="B112" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" t="s">
+        <v>18</v>
+      </c>
+      <c r="D112" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="1">
+        <v>183.21440100000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tensile_strength_clammp.xlsx
+++ b/tensile_strength_clammp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/graphene-oxide-paper-coatings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="8_{E7047EFC-AC87-1446-9EE2-AFD11443121C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B449AC5C-D5B9-F249-8F15-DFA47597011A}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="8_{E7047EFC-AC87-1446-9EE2-AFD11443121C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A37B31-4DC4-154E-AD19-E34238BB37FC}"/>
   <bookViews>
     <workbookView xWindow="1060" yWindow="1240" windowWidth="27640" windowHeight="16740" xr2:uid="{9D6F6D14-15C4-894F-A380-C8BF75B569C1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="19">
   <si>
     <t>Sample</t>
   </si>
@@ -484,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1161D6ED-F005-7245-AC8F-CA8CEF89B76D}">
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
@@ -2734,6 +2734,406 @@
         <v>183.21440100000001</v>
       </c>
     </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113">
+        <v>1</v>
+      </c>
+      <c r="B113" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="2">
+        <v>52.606754000000002</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114">
+        <v>2</v>
+      </c>
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="2">
+        <v>66.542145000000005</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115">
+        <v>3</v>
+      </c>
+      <c r="B115" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" s="2">
+        <v>67.156981999999999</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116">
+        <v>4</v>
+      </c>
+      <c r="B116" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" t="s">
+        <v>16</v>
+      </c>
+      <c r="E116" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" s="2">
+        <v>65.702720999999997</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117">
+        <v>5</v>
+      </c>
+      <c r="B117" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" t="s">
+        <v>9</v>
+      </c>
+      <c r="F117" s="2">
+        <v>79.301247000000004</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118">
+        <v>6</v>
+      </c>
+      <c r="B118" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" t="s">
+        <v>16</v>
+      </c>
+      <c r="E118" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="2">
+        <v>70.130882</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119">
+        <v>7</v>
+      </c>
+      <c r="B119" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" t="s">
+        <v>16</v>
+      </c>
+      <c r="E119" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" s="2">
+        <v>84.646827999999999</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120">
+        <v>8</v>
+      </c>
+      <c r="B120" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" s="2">
+        <v>74.772796999999997</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121">
+        <v>9</v>
+      </c>
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" t="s">
+        <v>17</v>
+      </c>
+      <c r="D121" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="2">
+        <v>68.441779999999994</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122">
+        <v>10</v>
+      </c>
+      <c r="B122" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" t="s">
+        <v>16</v>
+      </c>
+      <c r="E122" t="s">
+        <v>9</v>
+      </c>
+      <c r="F122" s="2">
+        <v>69.148674</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123">
+        <v>1</v>
+      </c>
+      <c r="B123" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" t="s">
+        <v>18</v>
+      </c>
+      <c r="D123" t="s">
+        <v>16</v>
+      </c>
+      <c r="E123" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="2">
+        <v>68.045074</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124">
+        <v>2</v>
+      </c>
+      <c r="B124" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" t="s">
+        <v>18</v>
+      </c>
+      <c r="D124" t="s">
+        <v>16</v>
+      </c>
+      <c r="E124" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="2">
+        <v>71.723831000000004</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125">
+        <v>3</v>
+      </c>
+      <c r="B125" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" t="s">
+        <v>18</v>
+      </c>
+      <c r="D125" t="s">
+        <v>16</v>
+      </c>
+      <c r="E125" t="s">
+        <v>9</v>
+      </c>
+      <c r="F125" s="2">
+        <v>59.385185</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126">
+        <v>4</v>
+      </c>
+      <c r="B126" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" t="s">
+        <v>18</v>
+      </c>
+      <c r="D126" t="s">
+        <v>16</v>
+      </c>
+      <c r="E126" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="2">
+        <v>69.775238000000002</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A127">
+        <v>5</v>
+      </c>
+      <c r="B127" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" t="s">
+        <v>18</v>
+      </c>
+      <c r="D127" t="s">
+        <v>16</v>
+      </c>
+      <c r="E127" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="2">
+        <v>76.287177999999997</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A128">
+        <v>6</v>
+      </c>
+      <c r="B128" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" t="s">
+        <v>18</v>
+      </c>
+      <c r="D128" t="s">
+        <v>16</v>
+      </c>
+      <c r="E128" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="2">
+        <v>69.871703999999994</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129">
+        <v>7</v>
+      </c>
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" t="s">
+        <v>18</v>
+      </c>
+      <c r="D129" t="s">
+        <v>16</v>
+      </c>
+      <c r="E129" t="s">
+        <v>9</v>
+      </c>
+      <c r="F129" s="2">
+        <v>64.807006999999999</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130">
+        <v>8</v>
+      </c>
+      <c r="B130" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" t="s">
+        <v>18</v>
+      </c>
+      <c r="D130" t="s">
+        <v>16</v>
+      </c>
+      <c r="E130" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130" s="2">
+        <v>58.587989999999998</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131">
+        <v>9</v>
+      </c>
+      <c r="B131" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" t="s">
+        <v>18</v>
+      </c>
+      <c r="D131" t="s">
+        <v>16</v>
+      </c>
+      <c r="E131" t="s">
+        <v>9</v>
+      </c>
+      <c r="F131" s="2">
+        <v>74.616530999999995</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132">
+        <v>10</v>
+      </c>
+      <c r="B132" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" t="s">
+        <v>18</v>
+      </c>
+      <c r="D132" t="s">
+        <v>16</v>
+      </c>
+      <c r="E132" t="s">
+        <v>9</v>
+      </c>
+      <c r="F132" s="2">
+        <v>63.845032000000003</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tensile_strength_clammp.xlsx
+++ b/tensile_strength_clammp.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/graphene-oxide-paper-coatings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="8_{E7047EFC-AC87-1446-9EE2-AFD11443121C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6A37B31-4DC4-154E-AD19-E34238BB37FC}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="8_{E7047EFC-AC87-1446-9EE2-AFD11443121C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23416DF0-F1FC-AB4F-9EC5-3EF5E45EF19B}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="1240" windowWidth="27640" windowHeight="16740" xr2:uid="{9D6F6D14-15C4-894F-A380-C8BF75B569C1}"/>
+    <workbookView xWindow="1060" yWindow="1200" windowWidth="27640" windowHeight="16740" xr2:uid="{9D6F6D14-15C4-894F-A380-C8BF75B569C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="20">
   <si>
     <t>Sample</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>25% WBBC + 0.1% GO</t>
+  </si>
+  <si>
+    <t>5% WBBC + 0.1% GO</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1161D6ED-F005-7245-AC8F-CA8CEF89B76D}">
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
@@ -3134,6 +3137,206 @@
         <v>63.845032000000003</v>
       </c>
     </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133">
+        <v>1</v>
+      </c>
+      <c r="B133" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" t="s">
+        <v>19</v>
+      </c>
+      <c r="D133" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" s="2">
+        <v>157.936646</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134">
+        <v>2</v>
+      </c>
+      <c r="B134" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" t="s">
+        <v>19</v>
+      </c>
+      <c r="D134" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" t="s">
+        <v>9</v>
+      </c>
+      <c r="F134" s="2">
+        <v>159.23902899999999</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135">
+        <v>3</v>
+      </c>
+      <c r="B135" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" s="2">
+        <v>155.947891</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136">
+        <v>4</v>
+      </c>
+      <c r="B136" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" s="2">
+        <v>155.43214399999999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137">
+        <v>5</v>
+      </c>
+      <c r="B137" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" t="s">
+        <v>19</v>
+      </c>
+      <c r="D137" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="2">
+        <v>145.32444799999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138">
+        <v>6</v>
+      </c>
+      <c r="B138" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" t="s">
+        <v>19</v>
+      </c>
+      <c r="D138" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" t="s">
+        <v>9</v>
+      </c>
+      <c r="F138" s="2">
+        <v>160.07551599999999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139">
+        <v>7</v>
+      </c>
+      <c r="B139" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" s="2">
+        <v>156.92131000000001</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140">
+        <v>8</v>
+      </c>
+      <c r="B140" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" s="2">
+        <v>149.19143700000001</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141">
+        <v>9</v>
+      </c>
+      <c r="B141" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" t="s">
+        <v>19</v>
+      </c>
+      <c r="D141" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" s="2">
+        <v>157.047943</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142">
+        <v>10</v>
+      </c>
+      <c r="B142" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142" t="s">
+        <v>8</v>
+      </c>
+      <c r="E142" t="s">
+        <v>9</v>
+      </c>
+      <c r="F142" s="2">
+        <v>149.899506</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tensile_strength_clammp.xlsx
+++ b/tensile_strength_clammp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/graphene-oxide-paper-coatings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="8_{E7047EFC-AC87-1446-9EE2-AFD11443121C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23416DF0-F1FC-AB4F-9EC5-3EF5E45EF19B}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="8_{E7047EFC-AC87-1446-9EE2-AFD11443121C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFD7635C-05BC-E849-81D8-E38438721123}"/>
   <bookViews>
-    <workbookView xWindow="1060" yWindow="1200" windowWidth="27640" windowHeight="16740" xr2:uid="{9D6F6D14-15C4-894F-A380-C8BF75B569C1}"/>
+    <workbookView xWindow="9320" yWindow="740" windowWidth="19580" windowHeight="16740" xr2:uid="{9D6F6D14-15C4-894F-A380-C8BF75B569C1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="28">
   <si>
     <t>Sample</t>
   </si>
@@ -97,6 +97,30 @@
   <si>
     <t>5% WBBC + 0.1% GO</t>
   </si>
+  <si>
+    <t>Greif</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>H4</t>
+  </si>
+  <si>
+    <t>H5</t>
+  </si>
+  <si>
+    <t>H6</t>
+  </si>
 </sst>
 </file>
 
@@ -105,7 +129,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -123,6 +147,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -146,13 +176,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="5"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -487,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1161D6ED-F005-7245-AC8F-CA8CEF89B76D}">
-  <dimension ref="A1:F142"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.33203125" customWidth="1"/>
@@ -3337,7 +3368,1208 @@
         <v>149.899506</v>
       </c>
     </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143">
+        <v>1</v>
+      </c>
+      <c r="B143" t="s">
+        <v>20</v>
+      </c>
+      <c r="C143" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143" t="s">
+        <v>16</v>
+      </c>
+      <c r="E143" t="s">
+        <v>22</v>
+      </c>
+      <c r="F143" s="4">
+        <v>37.324084999999997</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>20</v>
+      </c>
+      <c r="C144" t="s">
+        <v>21</v>
+      </c>
+      <c r="D144" t="s">
+        <v>16</v>
+      </c>
+      <c r="E144" t="s">
+        <v>22</v>
+      </c>
+      <c r="F144" s="4">
+        <v>35.377257999999998</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145">
+        <v>3</v>
+      </c>
+      <c r="B145" t="s">
+        <v>20</v>
+      </c>
+      <c r="C145" t="s">
+        <v>21</v>
+      </c>
+      <c r="D145" t="s">
+        <v>16</v>
+      </c>
+      <c r="E145" t="s">
+        <v>22</v>
+      </c>
+      <c r="F145" s="4">
+        <v>31.858585000000001</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146">
+        <v>4</v>
+      </c>
+      <c r="B146" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" t="s">
+        <v>16</v>
+      </c>
+      <c r="E146" t="s">
+        <v>22</v>
+      </c>
+      <c r="F146" s="4">
+        <v>32.996502</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147">
+        <v>5</v>
+      </c>
+      <c r="B147" t="s">
+        <v>20</v>
+      </c>
+      <c r="C147" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" t="s">
+        <v>16</v>
+      </c>
+      <c r="E147" t="s">
+        <v>22</v>
+      </c>
+      <c r="F147" s="4">
+        <v>33.666752000000002</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>6</v>
+      </c>
+      <c r="B148" t="s">
+        <v>20</v>
+      </c>
+      <c r="C148" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" t="s">
+        <v>16</v>
+      </c>
+      <c r="E148" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="4">
+        <v>32.717959999999998</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>7</v>
+      </c>
+      <c r="B149" t="s">
+        <v>20</v>
+      </c>
+      <c r="C149" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149" t="s">
+        <v>16</v>
+      </c>
+      <c r="E149" t="s">
+        <v>22</v>
+      </c>
+      <c r="F149" s="4">
+        <v>32.191375999999998</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>8</v>
+      </c>
+      <c r="B150" t="s">
+        <v>20</v>
+      </c>
+      <c r="C150" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" t="s">
+        <v>16</v>
+      </c>
+      <c r="E150" t="s">
+        <v>22</v>
+      </c>
+      <c r="F150" s="4">
+        <v>40.646908000000003</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>9</v>
+      </c>
+      <c r="B151" t="s">
+        <v>20</v>
+      </c>
+      <c r="C151" t="s">
+        <v>21</v>
+      </c>
+      <c r="D151" t="s">
+        <v>16</v>
+      </c>
+      <c r="E151" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" s="4">
+        <v>27.806004000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>10</v>
+      </c>
+      <c r="B152" t="s">
+        <v>20</v>
+      </c>
+      <c r="C152" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" t="s">
+        <v>16</v>
+      </c>
+      <c r="E152" t="s">
+        <v>22</v>
+      </c>
+      <c r="F152" s="4">
+        <v>34.827804999999998</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>1</v>
+      </c>
+      <c r="B153" t="s">
+        <v>20</v>
+      </c>
+      <c r="C153" t="s">
+        <v>23</v>
+      </c>
+      <c r="D153" t="s">
+        <v>16</v>
+      </c>
+      <c r="E153" t="s">
+        <v>22</v>
+      </c>
+      <c r="F153" s="4">
+        <v>66.501983999999993</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>2</v>
+      </c>
+      <c r="B154" t="s">
+        <v>20</v>
+      </c>
+      <c r="C154" t="s">
+        <v>23</v>
+      </c>
+      <c r="D154" t="s">
+        <v>16</v>
+      </c>
+      <c r="E154" t="s">
+        <v>22</v>
+      </c>
+      <c r="F154" s="4">
+        <v>69.138122999999993</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>3</v>
+      </c>
+      <c r="B155" t="s">
+        <v>20</v>
+      </c>
+      <c r="C155" t="s">
+        <v>23</v>
+      </c>
+      <c r="D155" t="s">
+        <v>16</v>
+      </c>
+      <c r="E155" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" s="4">
+        <v>64.416167999999999</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>4</v>
+      </c>
+      <c r="B156" t="s">
+        <v>20</v>
+      </c>
+      <c r="C156" t="s">
+        <v>23</v>
+      </c>
+      <c r="D156" t="s">
+        <v>16</v>
+      </c>
+      <c r="E156" t="s">
+        <v>22</v>
+      </c>
+      <c r="F156" s="4">
+        <v>54.797226000000002</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>5</v>
+      </c>
+      <c r="B157" t="s">
+        <v>20</v>
+      </c>
+      <c r="C157" t="s">
+        <v>23</v>
+      </c>
+      <c r="D157" t="s">
+        <v>16</v>
+      </c>
+      <c r="E157" t="s">
+        <v>22</v>
+      </c>
+      <c r="F157" s="4">
+        <v>62.679564999999997</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>6</v>
+      </c>
+      <c r="B158" t="s">
+        <v>20</v>
+      </c>
+      <c r="C158" t="s">
+        <v>23</v>
+      </c>
+      <c r="D158" t="s">
+        <v>16</v>
+      </c>
+      <c r="E158" t="s">
+        <v>22</v>
+      </c>
+      <c r="F158" s="4">
+        <v>63.034618000000002</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>7</v>
+      </c>
+      <c r="B159" t="s">
+        <v>20</v>
+      </c>
+      <c r="C159" t="s">
+        <v>23</v>
+      </c>
+      <c r="D159" t="s">
+        <v>16</v>
+      </c>
+      <c r="E159" t="s">
+        <v>22</v>
+      </c>
+      <c r="F159" s="4">
+        <v>67.452224999999999</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>8</v>
+      </c>
+      <c r="B160" t="s">
+        <v>20</v>
+      </c>
+      <c r="C160" t="s">
+        <v>23</v>
+      </c>
+      <c r="D160" t="s">
+        <v>16</v>
+      </c>
+      <c r="E160" t="s">
+        <v>22</v>
+      </c>
+      <c r="F160" s="4">
+        <v>59.786568000000003</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>9</v>
+      </c>
+      <c r="B161" t="s">
+        <v>20</v>
+      </c>
+      <c r="C161" t="s">
+        <v>23</v>
+      </c>
+      <c r="D161" t="s">
+        <v>16</v>
+      </c>
+      <c r="E161" t="s">
+        <v>22</v>
+      </c>
+      <c r="F161" s="4">
+        <v>58.901417000000002</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>10</v>
+      </c>
+      <c r="B162" t="s">
+        <v>20</v>
+      </c>
+      <c r="C162" t="s">
+        <v>23</v>
+      </c>
+      <c r="D162" t="s">
+        <v>16</v>
+      </c>
+      <c r="E162" t="s">
+        <v>22</v>
+      </c>
+      <c r="F162" s="4">
+        <v>52.207999999999998</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>1</v>
+      </c>
+      <c r="B163" t="s">
+        <v>20</v>
+      </c>
+      <c r="C163" t="s">
+        <v>24</v>
+      </c>
+      <c r="D163" t="s">
+        <v>16</v>
+      </c>
+      <c r="E163" t="s">
+        <v>22</v>
+      </c>
+      <c r="F163" s="4">
+        <v>31.986139000000001</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>20</v>
+      </c>
+      <c r="C164" t="s">
+        <v>24</v>
+      </c>
+      <c r="D164" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" s="4">
+        <v>33.233409999999999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>3</v>
+      </c>
+      <c r="B165" t="s">
+        <v>20</v>
+      </c>
+      <c r="C165" t="s">
+        <v>24</v>
+      </c>
+      <c r="D165" t="s">
+        <v>16</v>
+      </c>
+      <c r="E165" t="s">
+        <v>22</v>
+      </c>
+      <c r="F165" s="4">
+        <v>34.476844999999997</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>4</v>
+      </c>
+      <c r="B166" t="s">
+        <v>20</v>
+      </c>
+      <c r="C166" t="s">
+        <v>24</v>
+      </c>
+      <c r="D166" t="s">
+        <v>16</v>
+      </c>
+      <c r="E166" t="s">
+        <v>22</v>
+      </c>
+      <c r="F166" s="4">
+        <v>35.853703000000003</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>5</v>
+      </c>
+      <c r="B167" t="s">
+        <v>20</v>
+      </c>
+      <c r="C167" t="s">
+        <v>24</v>
+      </c>
+      <c r="D167" t="s">
+        <v>16</v>
+      </c>
+      <c r="E167" t="s">
+        <v>22</v>
+      </c>
+      <c r="F167" s="4">
+        <v>46.654240000000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>6</v>
+      </c>
+      <c r="B168" t="s">
+        <v>20</v>
+      </c>
+      <c r="C168" t="s">
+        <v>24</v>
+      </c>
+      <c r="D168" t="s">
+        <v>16</v>
+      </c>
+      <c r="E168" t="s">
+        <v>22</v>
+      </c>
+      <c r="F168" s="4">
+        <v>33.181797000000003</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>7</v>
+      </c>
+      <c r="B169" t="s">
+        <v>20</v>
+      </c>
+      <c r="C169" t="s">
+        <v>24</v>
+      </c>
+      <c r="D169" t="s">
+        <v>16</v>
+      </c>
+      <c r="E169" t="s">
+        <v>22</v>
+      </c>
+      <c r="F169" s="4">
+        <v>39.649151000000003</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>8</v>
+      </c>
+      <c r="B170" t="s">
+        <v>20</v>
+      </c>
+      <c r="C170" t="s">
+        <v>24</v>
+      </c>
+      <c r="D170" t="s">
+        <v>16</v>
+      </c>
+      <c r="E170" t="s">
+        <v>22</v>
+      </c>
+      <c r="F170" s="4">
+        <v>39.530991</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>9</v>
+      </c>
+      <c r="B171" t="s">
+        <v>20</v>
+      </c>
+      <c r="C171" t="s">
+        <v>24</v>
+      </c>
+      <c r="D171" t="s">
+        <v>16</v>
+      </c>
+      <c r="E171" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="4">
+        <v>38.457596000000002</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>10</v>
+      </c>
+      <c r="B172" t="s">
+        <v>20</v>
+      </c>
+      <c r="C172" t="s">
+        <v>24</v>
+      </c>
+      <c r="D172" t="s">
+        <v>16</v>
+      </c>
+      <c r="E172" t="s">
+        <v>22</v>
+      </c>
+      <c r="F172" s="4">
+        <v>26.480467000000001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>1</v>
+      </c>
+      <c r="B173" t="s">
+        <v>20</v>
+      </c>
+      <c r="C173" t="s">
+        <v>25</v>
+      </c>
+      <c r="D173" t="s">
+        <v>16</v>
+      </c>
+      <c r="E173" t="s">
+        <v>22</v>
+      </c>
+      <c r="F173" s="4">
+        <v>45.241024000000003</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>2</v>
+      </c>
+      <c r="B174" t="s">
+        <v>20</v>
+      </c>
+      <c r="C174" t="s">
+        <v>25</v>
+      </c>
+      <c r="D174" t="s">
+        <v>16</v>
+      </c>
+      <c r="E174" t="s">
+        <v>22</v>
+      </c>
+      <c r="F174" s="4">
+        <v>41.753138999999997</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>3</v>
+      </c>
+      <c r="B175" t="s">
+        <v>20</v>
+      </c>
+      <c r="C175" t="s">
+        <v>25</v>
+      </c>
+      <c r="D175" t="s">
+        <v>16</v>
+      </c>
+      <c r="E175" t="s">
+        <v>22</v>
+      </c>
+      <c r="F175" s="4">
+        <v>41.525627</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>4</v>
+      </c>
+      <c r="B176" t="s">
+        <v>20</v>
+      </c>
+      <c r="C176" t="s">
+        <v>25</v>
+      </c>
+      <c r="D176" t="s">
+        <v>16</v>
+      </c>
+      <c r="E176" t="s">
+        <v>22</v>
+      </c>
+      <c r="F176" s="4">
+        <v>38.990929000000001</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>5</v>
+      </c>
+      <c r="B177" t="s">
+        <v>20</v>
+      </c>
+      <c r="C177" t="s">
+        <v>25</v>
+      </c>
+      <c r="D177" t="s">
+        <v>16</v>
+      </c>
+      <c r="E177" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" s="4">
+        <v>37.329666000000003</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>6</v>
+      </c>
+      <c r="B178" t="s">
+        <v>20</v>
+      </c>
+      <c r="C178" t="s">
+        <v>25</v>
+      </c>
+      <c r="D178" t="s">
+        <v>16</v>
+      </c>
+      <c r="E178" t="s">
+        <v>22</v>
+      </c>
+      <c r="F178" s="4">
+        <v>53.597458000000003</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>7</v>
+      </c>
+      <c r="B179" t="s">
+        <v>20</v>
+      </c>
+      <c r="C179" t="s">
+        <v>25</v>
+      </c>
+      <c r="D179" t="s">
+        <v>16</v>
+      </c>
+      <c r="E179" t="s">
+        <v>22</v>
+      </c>
+      <c r="F179" s="4">
+        <v>41.192261000000002</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>8</v>
+      </c>
+      <c r="B180" t="s">
+        <v>20</v>
+      </c>
+      <c r="C180" t="s">
+        <v>25</v>
+      </c>
+      <c r="D180" t="s">
+        <v>16</v>
+      </c>
+      <c r="E180" t="s">
+        <v>22</v>
+      </c>
+      <c r="F180" s="4">
+        <v>45.030799999999999</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>9</v>
+      </c>
+      <c r="B181" t="s">
+        <v>20</v>
+      </c>
+      <c r="C181" t="s">
+        <v>25</v>
+      </c>
+      <c r="D181" t="s">
+        <v>16</v>
+      </c>
+      <c r="E181" t="s">
+        <v>22</v>
+      </c>
+      <c r="F181" s="4">
+        <v>50.374924</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>10</v>
+      </c>
+      <c r="B182" t="s">
+        <v>20</v>
+      </c>
+      <c r="C182" t="s">
+        <v>25</v>
+      </c>
+      <c r="D182" t="s">
+        <v>16</v>
+      </c>
+      <c r="E182" t="s">
+        <v>22</v>
+      </c>
+      <c r="F182" s="4">
+        <v>41.928485999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>1</v>
+      </c>
+      <c r="B183" t="s">
+        <v>20</v>
+      </c>
+      <c r="C183" t="s">
+        <v>26</v>
+      </c>
+      <c r="D183" t="s">
+        <v>16</v>
+      </c>
+      <c r="E183" t="s">
+        <v>22</v>
+      </c>
+      <c r="F183" s="4">
+        <v>47.305137999999999</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>2</v>
+      </c>
+      <c r="B184" t="s">
+        <v>20</v>
+      </c>
+      <c r="C184" t="s">
+        <v>26</v>
+      </c>
+      <c r="D184" t="s">
+        <v>16</v>
+      </c>
+      <c r="E184" t="s">
+        <v>22</v>
+      </c>
+      <c r="F184" s="4">
+        <v>43.196857000000001</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>3</v>
+      </c>
+      <c r="B185" t="s">
+        <v>20</v>
+      </c>
+      <c r="C185" t="s">
+        <v>26</v>
+      </c>
+      <c r="D185" t="s">
+        <v>16</v>
+      </c>
+      <c r="E185" t="s">
+        <v>22</v>
+      </c>
+      <c r="F185" s="4">
+        <v>43.796146</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>4</v>
+      </c>
+      <c r="B186" t="s">
+        <v>20</v>
+      </c>
+      <c r="C186" t="s">
+        <v>26</v>
+      </c>
+      <c r="D186" t="s">
+        <v>16</v>
+      </c>
+      <c r="E186" t="s">
+        <v>22</v>
+      </c>
+      <c r="F186" s="4">
+        <v>43.036468999999997</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>5</v>
+      </c>
+      <c r="B187" t="s">
+        <v>20</v>
+      </c>
+      <c r="C187" t="s">
+        <v>26</v>
+      </c>
+      <c r="D187" t="s">
+        <v>16</v>
+      </c>
+      <c r="E187" t="s">
+        <v>22</v>
+      </c>
+      <c r="F187" s="4">
+        <v>46.681221000000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>6</v>
+      </c>
+      <c r="B188" t="s">
+        <v>20</v>
+      </c>
+      <c r="C188" t="s">
+        <v>26</v>
+      </c>
+      <c r="D188" t="s">
+        <v>16</v>
+      </c>
+      <c r="E188" t="s">
+        <v>22</v>
+      </c>
+      <c r="F188" s="4">
+        <v>39.096770999999997</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>7</v>
+      </c>
+      <c r="B189" t="s">
+        <v>20</v>
+      </c>
+      <c r="C189" t="s">
+        <v>26</v>
+      </c>
+      <c r="D189" t="s">
+        <v>16</v>
+      </c>
+      <c r="E189" t="s">
+        <v>22</v>
+      </c>
+      <c r="F189" s="4">
+        <v>47.531193000000002</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>8</v>
+      </c>
+      <c r="B190" t="s">
+        <v>20</v>
+      </c>
+      <c r="C190" t="s">
+        <v>26</v>
+      </c>
+      <c r="D190" t="s">
+        <v>16</v>
+      </c>
+      <c r="E190" t="s">
+        <v>22</v>
+      </c>
+      <c r="F190" s="4">
+        <v>51.535983999999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>9</v>
+      </c>
+      <c r="B191" t="s">
+        <v>20</v>
+      </c>
+      <c r="C191" t="s">
+        <v>26</v>
+      </c>
+      <c r="D191" t="s">
+        <v>16</v>
+      </c>
+      <c r="E191" t="s">
+        <v>22</v>
+      </c>
+      <c r="F191" s="4">
+        <v>46.315894999999998</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>10</v>
+      </c>
+      <c r="B192" t="s">
+        <v>20</v>
+      </c>
+      <c r="C192" t="s">
+        <v>26</v>
+      </c>
+      <c r="D192" t="s">
+        <v>16</v>
+      </c>
+      <c r="E192" t="s">
+        <v>22</v>
+      </c>
+      <c r="F192" s="4">
+        <v>41.024849000000003</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>1</v>
+      </c>
+      <c r="B193" t="s">
+        <v>20</v>
+      </c>
+      <c r="C193" t="s">
+        <v>27</v>
+      </c>
+      <c r="D193" t="s">
+        <v>16</v>
+      </c>
+      <c r="E193" t="s">
+        <v>22</v>
+      </c>
+      <c r="F193" s="4">
+        <v>63.579673999999997</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>2</v>
+      </c>
+      <c r="B194" t="s">
+        <v>20</v>
+      </c>
+      <c r="C194" t="s">
+        <v>27</v>
+      </c>
+      <c r="D194" t="s">
+        <v>16</v>
+      </c>
+      <c r="E194" t="s">
+        <v>22</v>
+      </c>
+      <c r="F194" s="4">
+        <v>68.363495</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>3</v>
+      </c>
+      <c r="B195" t="s">
+        <v>20</v>
+      </c>
+      <c r="C195" t="s">
+        <v>27</v>
+      </c>
+      <c r="D195" t="s">
+        <v>16</v>
+      </c>
+      <c r="E195" t="s">
+        <v>22</v>
+      </c>
+      <c r="F195" s="4">
+        <v>60.114666</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>4</v>
+      </c>
+      <c r="B196" t="s">
+        <v>20</v>
+      </c>
+      <c r="C196" t="s">
+        <v>27</v>
+      </c>
+      <c r="D196" t="s">
+        <v>16</v>
+      </c>
+      <c r="E196" t="s">
+        <v>22</v>
+      </c>
+      <c r="F196" s="4">
+        <v>61.386260999999998</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>5</v>
+      </c>
+      <c r="B197" t="s">
+        <v>20</v>
+      </c>
+      <c r="C197" t="s">
+        <v>27</v>
+      </c>
+      <c r="D197" t="s">
+        <v>16</v>
+      </c>
+      <c r="E197" t="s">
+        <v>22</v>
+      </c>
+      <c r="F197" s="4">
+        <v>57.774062999999998</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>6</v>
+      </c>
+      <c r="B198" t="s">
+        <v>20</v>
+      </c>
+      <c r="C198" t="s">
+        <v>27</v>
+      </c>
+      <c r="D198" t="s">
+        <v>16</v>
+      </c>
+      <c r="E198" t="s">
+        <v>22</v>
+      </c>
+      <c r="F198" s="4">
+        <v>58.066977999999999</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>7</v>
+      </c>
+      <c r="B199" t="s">
+        <v>20</v>
+      </c>
+      <c r="C199" t="s">
+        <v>27</v>
+      </c>
+      <c r="D199" t="s">
+        <v>16</v>
+      </c>
+      <c r="E199" t="s">
+        <v>22</v>
+      </c>
+      <c r="F199" s="4">
+        <v>59.643208000000001</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>8</v>
+      </c>
+      <c r="B200" t="s">
+        <v>20</v>
+      </c>
+      <c r="C200" t="s">
+        <v>27</v>
+      </c>
+      <c r="D200" t="s">
+        <v>16</v>
+      </c>
+      <c r="E200" t="s">
+        <v>22</v>
+      </c>
+      <c r="F200" s="4">
+        <v>59.827930000000002</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>9</v>
+      </c>
+      <c r="B201" t="s">
+        <v>20</v>
+      </c>
+      <c r="C201" t="s">
+        <v>27</v>
+      </c>
+      <c r="D201" t="s">
+        <v>16</v>
+      </c>
+      <c r="E201" t="s">
+        <v>22</v>
+      </c>
+      <c r="F201" s="4">
+        <v>62.918807999999999</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>10</v>
+      </c>
+      <c r="B202" t="s">
+        <v>20</v>
+      </c>
+      <c r="C202" t="s">
+        <v>27</v>
+      </c>
+      <c r="D202" t="s">
+        <v>16</v>
+      </c>
+      <c r="E202" t="s">
+        <v>22</v>
+      </c>
+      <c r="F202" s="4">
+        <v>59.816493999999999</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>